--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">501384, 5781087, 501385</t>
+          <t xml:space="preserve">308336, 308337</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>9658</v>
+        <v>4431</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5258778</t>
+          <t xml:space="preserve">312395</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>525</v>
+        <v>3239</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">312396</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F10">
-        <v>2320</v>
+        <v>4941</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278661</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F11">
-        <v>480</v>
+        <v>6688</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F12">
-        <v>599</v>
+        <v>975</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281255</t>
+          <t xml:space="preserve">501384, 5781087, 501385</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>304</v>
+        <v>9658</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5286928</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F14">
-        <v>1065</v>
+        <v>2320</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287023</t>
+          <t xml:space="preserve">5278661</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F15">
-        <v>329</v>
+        <v>480</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287570</t>
+          <t xml:space="preserve">5281255</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295391</t>
+          <t xml:space="preserve">5286928</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>1535</v>
+        <v>1065</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5296567</t>
+          <t xml:space="preserve">5287023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>823</v>
+        <v>329</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5296575</t>
+          <t xml:space="preserve">5295391</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>314</v>
+        <v>1535</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298208</t>
+          <t xml:space="preserve">5296567</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>330</v>
+        <v>823</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781097</t>
+          <t xml:space="preserve">5296575</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>602</v>
+        <v>314</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781256</t>
+          <t xml:space="preserve">5298208</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F22">
-        <v>836</v>
+        <v>330</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784885</t>
+          <t xml:space="preserve">5781097</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784885</t>
+          <t xml:space="preserve">5781256</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F24">
-        <v>738</v>
+        <v>836</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785626</t>
+          <t xml:space="preserve">5784885</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>1471</v>
+        <v>602</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">5784885</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F26">
-        <v>2778</v>
+        <v>738</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">735305, 5287162</t>
+          <t xml:space="preserve">5785626</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>317</v>
+        <v>1471</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">735313, 8953911</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F28">
-        <v>1953</v>
+        <v>2778</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">735395, 5258385</t>
+          <t xml:space="preserve">735305, 5287162</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">735313, 8953911</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>1717</v>
+        <v>1953</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">735395, 5258385</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>624</v>
+        <v>362</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8111599</t>
+          <t xml:space="preserve">9022305</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F47">
-        <v>329</v>
+        <v>430</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,30 +2381,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8166350</t>
+          <t xml:space="preserve">5787622</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>1494</v>
+        <v>1001</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200009991</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-01-15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5787788</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="F49">
-        <v>340</v>
+        <v>1857</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010534</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-09</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2481,30 +2481,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5785700</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>752</v>
+        <v>336</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010697</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5285761</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>996</v>
+        <v>364</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011492</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2581,30 +2581,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5285444</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>310</v>
+        <v>1217</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011536</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2631,30 +2631,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022305</t>
+          <t xml:space="preserve">5783138</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>430</v>
+        <v>1072</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011633</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787622</t>
+          <t xml:space="preserve">5295266</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>1001</v>
+        <v>9679</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009991</t>
+          <t xml:space="preserve">200012359</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-01-15</t>
+          <t xml:space="preserve">2019-04-07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787788</t>
+          <t xml:space="preserve">7967180</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,16 +2740,16 @@
         </is>
       </c>
       <c r="F55">
-        <v>1857</v>
+        <v>1682</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010534</t>
+          <t xml:space="preserve">200012502</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-09</t>
+          <t xml:space="preserve">2019-04-15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785700</t>
+          <t xml:space="preserve">5292892</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>336</v>
+        <v>905</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010697</t>
+          <t xml:space="preserve">200012601</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-17</t>
+          <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285761</t>
+          <t xml:space="preserve">9665069</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>364</v>
+        <v>686</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011492</t>
+          <t xml:space="preserve">200012921</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-16</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285444</t>
+          <t xml:space="preserve">1512218</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,16 +2890,16 @@
         </is>
       </c>
       <c r="F58">
-        <v>1217</v>
+        <v>6492</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011536</t>
+          <t xml:space="preserve">200014764</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-17</t>
+          <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783138</t>
+          <t xml:space="preserve">5259087</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>1072</v>
+        <v>735</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011633</t>
+          <t xml:space="preserve">200016722</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-18</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295266</t>
+          <t xml:space="preserve">5272978</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="F60">
-        <v>9679</v>
+        <v>499</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012359</t>
+          <t xml:space="preserve">200017325</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-07</t>
+          <t xml:space="preserve">2019-07-09</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967180</t>
+          <t xml:space="preserve">9151738</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>1682</v>
+        <v>362</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012502</t>
+          <t xml:space="preserve">100127221</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-15</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292892</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="F62">
-        <v>905</v>
+        <v>340</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012601</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-17</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665069</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F63">
-        <v>686</v>
+        <v>752</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012921</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512218</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F64">
-        <v>6492</v>
+        <v>996</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014764</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-10</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259087</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F65">
-        <v>735</v>
+        <v>310</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016722</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272978</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F66">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017325</t>
+          <t xml:space="preserve">200018102</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-09</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151738</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100127221</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>529</v>
+        <v>573</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018102</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">5292814</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>274</v>
+        <v>4679</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200023568</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-11-08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">5787053</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>573</v>
+        <v>361</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200023607</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292814</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F71">
-        <v>4679</v>
+        <v>4233</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023568</t>
+          <t xml:space="preserve">200023653</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-08</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787053</t>
+          <t xml:space="preserve">8111599</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F72">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023607</t>
+          <t xml:space="preserve">200023651</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-09</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F73">
-        <v>4233</v>
+        <v>1717</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023653</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917210</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F74">
-        <v>1325</v>
+        <v>624</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023827</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,20 +3731,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787473</t>
+          <t xml:space="preserve">5287570</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029940</t>
+          <t xml:space="preserve">200029910</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870345</t>
+          <t xml:space="preserve">5787473</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>579</v>
+        <v>296</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030269</t>
+          <t xml:space="preserve">200029940</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-13</t>
+          <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">7870345</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>4816</v>
+        <v>579</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000776</t>
+          <t xml:space="preserve">200030269</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-27</t>
+          <t xml:space="preserve">2020-04-13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019921</t>
+          <t xml:space="preserve">5258778</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>7293</v>
+        <v>525</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311005752</t>
+          <t xml:space="preserve">200031045</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-26</t>
+          <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F79">
-        <v>1276</v>
+        <v>4816</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301220</t>
+          <t xml:space="preserve">310000776</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2022-06-27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3981,35 +3981,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">8166350</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F80">
-        <v>4367</v>
+        <v>1494</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301223</t>
+          <t xml:space="preserve">311041979</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2024-03-10</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10185368</t>
+          <t xml:space="preserve">100019921</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,26 +4040,26 @@
         </is>
       </c>
       <c r="F81">
-        <v>984</v>
+        <v>7293</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301595</t>
+          <t xml:space="preserve">311086983</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-08</t>
+          <t xml:space="preserve">2024-12-08</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>1740</v>
+        <v>1276</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332174</t>
+          <t xml:space="preserve">311301220</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-23</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072481</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>290</v>
+        <v>4367</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373248</t>
+          <t xml:space="preserve">311301223</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-26</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783317</t>
+          <t xml:space="preserve">10185368</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="F84">
-        <v>1702</v>
+        <v>984</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436294</t>
+          <t xml:space="preserve">311370738</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-06</t>
+          <t xml:space="preserve">2029-04-11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8583585</t>
+          <t xml:space="preserve">9072481</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>522</v>
+        <v>290</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498594</t>
+          <t xml:space="preserve">311373248</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2029-04-26</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5783317</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F86">
-        <v>10229</v>
+        <v>1702</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521350</t>
+          <t xml:space="preserve">311436294</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">8917210</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F87">
-        <v>6889</v>
+        <v>1325</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311495939</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">8583585</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F88">
-        <v>1468</v>
+        <v>522</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311498594</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4436,15 +4436,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F89">
-        <v>1157</v>
+        <v>10229</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521353</t>
+          <t xml:space="preserve">311521350</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>1583</v>
+        <v>6889</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560183</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F91">
-        <v>261</v>
+        <v>1468</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560181</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F92">
-        <v>689</v>
+        <v>1157</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560185</t>
+          <t xml:space="preserve">311521353</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4636,11 +4636,11 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>1198</v>
+        <v>1583</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4686,15 +4686,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F94">
-        <v>402</v>
+        <v>599</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560182</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4736,15 +4736,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>5032</v>
+        <v>261</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560184</t>
+          <t xml:space="preserve">311560181</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4786,15 +4786,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F96">
-        <v>560</v>
+        <v>689</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560186</t>
+          <t xml:space="preserve">311560185</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F97">
-        <v>9839</v>
+        <v>1198</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F98">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311560182</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8175481</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F99">
-        <v>776</v>
+        <v>5032</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560963</t>
+          <t xml:space="preserve">311560184</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F100">
-        <v>10333</v>
+        <v>560</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568970</t>
+          <t xml:space="preserve">311560186</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F101">
-        <v>3913</v>
+        <v>1740</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568975</t>
+          <t xml:space="preserve">311560982</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F102">
-        <v>500</v>
+        <v>9839</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568971</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786366</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F103">
-        <v>355</v>
+        <v>487</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652254</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">312395</t>
+          <t xml:space="preserve">8175481</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>3239</v>
+        <v>776</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661619</t>
+          <t xml:space="preserve">311560963</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">312396</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105">
-        <v>4941</v>
+        <v>10333</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661618</t>
+          <t xml:space="preserve">311568970</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>6688</v>
+        <v>3913</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661617</t>
+          <t xml:space="preserve">311568975</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F107">
-        <v>975</v>
+        <v>500</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661616</t>
+          <t xml:space="preserve">311568971</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290028</t>
+          <t xml:space="preserve">5786366</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>3620</v>
+        <v>355</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311652254</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5436,15 +5436,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>281</v>
+        <v>3620</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5486,15 +5486,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F110">
-        <v>1433</v>
+        <v>281</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022207</t>
+          <t xml:space="preserve">5290028</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F111">
-        <v>5131</v>
+        <v>1433</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674521</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-18</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5586,11 +5586,11 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>5091</v>
+        <v>5131</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5636,11 +5636,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F113">
-        <v>775</v>
+        <v>5091</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275405</t>
+          <t xml:space="preserve">9022207</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F114">
-        <v>1266</v>
+        <v>775</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675319</t>
+          <t xml:space="preserve">311674521</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5736,11 +5736,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F115">
-        <v>1041</v>
+        <v>1266</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5786,11 +5786,11 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>831</v>
+        <v>1041</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5836,11 +5836,11 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F117">
-        <v>1054</v>
+        <v>831</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5886,11 +5886,11 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F118">
-        <v>2025</v>
+        <v>1054</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5936,11 +5936,11 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F119">
-        <v>331</v>
+        <v>2025</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5986,11 +5986,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F120">
-        <v>684</v>
+        <v>331</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5276459</t>
+          <t xml:space="preserve">5275405</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F121">
-        <v>1833</v>
+        <v>684</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677211</t>
+          <t xml:space="preserve">311675319</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-28</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6086,11 +6086,11 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F122">
-        <v>1297</v>
+        <v>1833</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6136,20 +6136,20 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F123">
-        <v>490</v>
+        <v>1297</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677640</t>
+          <t xml:space="preserve">311677211</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6186,15 +6186,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>702</v>
+        <v>490</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677608</t>
+          <t xml:space="preserve">311677640</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8954042</t>
+          <t xml:space="preserve">5276459</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F125">
-        <v>1345</v>
+        <v>702</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311677608</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-09</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6286,11 +6286,11 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F126">
-        <v>822</v>
+        <v>1345</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6336,15 +6336,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F127">
-        <v>1707</v>
+        <v>822</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6386,15 +6386,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F128">
-        <v>462</v>
+        <v>1707</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6436,15 +6436,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F129">
-        <v>2353</v>
+        <v>462</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6486,11 +6486,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="F130">
-        <v>1906</v>
+        <v>2353</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6536,15 +6536,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F131">
-        <v>390</v>
+        <v>1906</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686708</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6586,15 +6586,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F132">
-        <v>1691</v>
+        <v>390</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686708</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6636,11 +6636,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F133">
-        <v>725</v>
+        <v>1691</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292219</t>
+          <t xml:space="preserve">8954042</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F134">
-        <v>1110</v>
+        <v>725</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690728</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-26</t>
+          <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6736,15 +6736,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F135">
-        <v>1045</v>
+        <v>1110</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690729</t>
+          <t xml:space="preserve">311690728</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257652</t>
+          <t xml:space="preserve">5292219</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F136">
-        <v>531</v>
+        <v>1045</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692727</t>
+          <t xml:space="preserve">311690729</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-04</t>
+          <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6836,20 +6836,20 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F137">
-        <v>6400</v>
+        <v>531</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311693153</t>
+          <t xml:space="preserve">311692727</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-05</t>
+          <t xml:space="preserve">2033-07-04</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257645</t>
+          <t xml:space="preserve">5257652</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>2539</v>
+        <v>6400</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696049</t>
+          <t xml:space="preserve">311693153</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-20</t>
+          <t xml:space="preserve">2033-07-05</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6936,11 +6936,11 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>1312</v>
+        <v>2539</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6986,20 +6986,20 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F140">
-        <v>1233</v>
+        <v>1312</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696243</t>
+          <t xml:space="preserve">311696049</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-21</t>
+          <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7036,15 +7036,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F141">
-        <v>2210</v>
+        <v>1233</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696184</t>
+          <t xml:space="preserve">311696243</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7086,15 +7086,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F142">
-        <v>1981</v>
+        <v>2210</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696280</t>
+          <t xml:space="preserve">311696184</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7136,20 +7136,20 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F143">
-        <v>501</v>
+        <v>1981</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696375</t>
+          <t xml:space="preserve">311696280</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-24</t>
+          <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7186,20 +7186,20 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F144">
-        <v>737</v>
+        <v>501</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697276</t>
+          <t xml:space="preserve">311696375</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-31</t>
+          <t xml:space="preserve">2033-07-24</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7236,15 +7236,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F145">
-        <v>252</v>
+        <v>737</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697270</t>
+          <t xml:space="preserve">311697276</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784337</t>
+          <t xml:space="preserve">5257645</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F146">
-        <v>5859</v>
+        <v>252</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698797</t>
+          <t xml:space="preserve">311697270</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5782338</t>
+          <t xml:space="preserve">5784337</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F147">
-        <v>5091</v>
+        <v>5859</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717581</t>
+          <t xml:space="preserve">311698797</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7386,15 +7386,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F148">
-        <v>800</v>
+        <v>5091</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717585</t>
+          <t xml:space="preserve">311717580</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7431,20 +7431,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7181513</t>
+          <t xml:space="preserve">5782338</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F149">
-        <v>267</v>
+        <v>800</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717579</t>
+          <t xml:space="preserve">311717580</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257481</t>
+          <t xml:space="preserve">7181513</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="F150">
-        <v>4554</v>
+        <v>267</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758410</t>
+          <t xml:space="preserve">311717579</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7536,11 +7536,11 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>397</v>
+        <v>4554</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275746</t>
+          <t xml:space="preserve">5257481</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F152">
-        <v>1497</v>
+        <v>397</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758407</t>
+          <t xml:space="preserve">311758410</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294806</t>
+          <t xml:space="preserve">5275746</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>617</v>
+        <v>1497</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761630</t>
+          <t xml:space="preserve">311758407</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-24</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294810</t>
+          <t xml:space="preserve">5294806</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,11 +7690,11 @@
         </is>
       </c>
       <c r="F154">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761633</t>
+          <t xml:space="preserve">311761630</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7846650</t>
+          <t xml:space="preserve">5294810</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,11 +7740,11 @@
         </is>
       </c>
       <c r="F155">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761632</t>
+          <t xml:space="preserve">311761633</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7786,11 +7786,11 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>1220</v>
+        <v>597</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281873</t>
+          <t xml:space="preserve">7846650</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F157">
-        <v>1305</v>
+        <v>1220</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762260</t>
+          <t xml:space="preserve">311761632</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7886,11 +7886,11 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>429</v>
+        <v>1305</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7936,11 +7936,11 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F159">
-        <v>592</v>
+        <v>429</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7981,20 +7981,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955245</t>
+          <t xml:space="preserve">5281873</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F160">
-        <v>6013</v>
+        <v>592</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762255</t>
+          <t xml:space="preserve">311762260</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8036,15 +8036,15 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F161">
-        <v>1449</v>
+        <v>6013</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762253</t>
+          <t xml:space="preserve">311762255</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294181</t>
+          <t xml:space="preserve">8955245</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F162">
-        <v>2590</v>
+        <v>1449</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311762253</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8136,15 +8136,15 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>329</v>
+        <v>2590</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766886</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8186,15 +8186,15 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>4077</v>
+        <v>329</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311766886</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8236,15 +8236,15 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F165">
-        <v>1160</v>
+        <v>4077</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766887</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8286,15 +8286,15 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F166">
-        <v>606</v>
+        <v>1160</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311766887</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562993</t>
+          <t xml:space="preserve">5294181</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F167">
-        <v>1425</v>
+        <v>606</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771819</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-05</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272155</t>
+          <t xml:space="preserve">9562993</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F168">
-        <v>1794</v>
+        <v>1425</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788055</t>
+          <t xml:space="preserve">311771819</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-27</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8436,15 +8436,15 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>779</v>
+        <v>1794</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788056</t>
+          <t xml:space="preserve">311788055</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8481,20 +8481,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272862</t>
+          <t xml:space="preserve">5272155</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F170">
-        <v>533</v>
+        <v>779</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788048</t>
+          <t xml:space="preserve">311788056</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">5272862</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8540,11 +8540,11 @@
         </is>
       </c>
       <c r="F171">
-        <v>2404</v>
+        <v>533</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788048</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8586,11 +8586,11 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F172">
-        <v>676</v>
+        <v>2404</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -8636,11 +8636,11 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F173">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8515752</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F174">
-        <v>532</v>
+        <v>690</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788047</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">8515752</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>1764</v>
+        <v>532</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797326</t>
+          <t xml:space="preserve">311788047</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8786,15 +8786,15 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F176">
-        <v>1210</v>
+        <v>1764</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797324</t>
+          <t xml:space="preserve">311797326</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8836,11 +8836,11 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F177">
-        <v>1828</v>
+        <v>1210</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -8886,11 +8886,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>1210</v>
+        <v>1828</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8936,15 +8936,15 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F179">
-        <v>266</v>
+        <v>1210</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797325</t>
+          <t xml:space="preserve">311797324</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278117</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F180">
-        <v>745</v>
+        <v>266</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311799237</t>
+          <t xml:space="preserve">311797325</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-25</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">5278117</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>2643</v>
+        <v>745</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800213</t>
+          <t xml:space="preserve">311799237</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-29</t>
+          <t xml:space="preserve">2034-11-25</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9086,15 +9086,15 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>609</v>
+        <v>2643</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800215</t>
+          <t xml:space="preserve">311800213</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9136,15 +9136,15 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F183">
-        <v>2605</v>
+        <v>609</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800217</t>
+          <t xml:space="preserve">311800215</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512200</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F184">
-        <v>2901</v>
+        <v>2605</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803350</t>
+          <t xml:space="preserve">311800217</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278572</t>
+          <t xml:space="preserve">1512200</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,11 +9240,11 @@
         </is>
       </c>
       <c r="F185">
-        <v>917</v>
+        <v>2901</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803369</t>
+          <t xml:space="preserve">311803350</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5279082</t>
+          <t xml:space="preserve">5278572</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9290,11 +9290,11 @@
         </is>
       </c>
       <c r="F186">
-        <v>382</v>
+        <v>917</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803358</t>
+          <t xml:space="preserve">311803369</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781025</t>
+          <t xml:space="preserve">5279082</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9340,11 +9340,11 @@
         </is>
       </c>
       <c r="F187">
-        <v>1339</v>
+        <v>382</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803378</t>
+          <t xml:space="preserve">311803358</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -9386,15 +9386,15 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F188">
-        <v>317</v>
+        <v>1339</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803381</t>
+          <t xml:space="preserve">311803378</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9431,20 +9431,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781423</t>
+          <t xml:space="preserve">5781025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F189">
-        <v>1859</v>
+        <v>317</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803364</t>
+          <t xml:space="preserve">311803381</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787147</t>
+          <t xml:space="preserve">5781423</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9490,11 +9490,11 @@
         </is>
       </c>
       <c r="F190">
-        <v>385</v>
+        <v>1859</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803395</t>
+          <t xml:space="preserve">311803364</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787761</t>
+          <t xml:space="preserve">5787147</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9540,11 +9540,11 @@
         </is>
       </c>
       <c r="F191">
-        <v>4402</v>
+        <v>385</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803385</t>
+          <t xml:space="preserve">311803395</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940680</t>
+          <t xml:space="preserve">5787761</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="F192">
-        <v>485</v>
+        <v>4402</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803387</t>
+          <t xml:space="preserve">311803385</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995417</t>
+          <t xml:space="preserve">8940680</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9640,11 +9640,11 @@
         </is>
       </c>
       <c r="F193">
-        <v>604</v>
+        <v>485</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803386</t>
+          <t xml:space="preserve">311803387</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275696</t>
+          <t xml:space="preserve">8995417</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,16 +9690,16 @@
         </is>
       </c>
       <c r="F194">
-        <v>385</v>
+        <v>604</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803590</t>
+          <t xml:space="preserve">311803386</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-19</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294114</t>
+          <t xml:space="preserve">5275696</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9740,11 +9740,11 @@
         </is>
       </c>
       <c r="F195">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803601</t>
+          <t xml:space="preserve">311803590</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787784</t>
+          <t xml:space="preserve">5294114</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,11 +9790,11 @@
         </is>
       </c>
       <c r="F196">
-        <v>868</v>
+        <v>288</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803725</t>
+          <t xml:space="preserve">311803601</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5286834</t>
+          <t xml:space="preserve">5787784</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9840,16 +9840,16 @@
         </is>
       </c>
       <c r="F197">
-        <v>365</v>
+        <v>868</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809080</t>
+          <t xml:space="preserve">311803725</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784905</t>
+          <t xml:space="preserve">5286834</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F198">
-        <v>476</v>
+        <v>365</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809348</t>
+          <t xml:space="preserve">311809080</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-03</t>
+          <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9936,15 +9936,15 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F199">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809350</t>
+          <t xml:space="preserve">311809348</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9986,15 +9986,15 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F200">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809346</t>
+          <t xml:space="preserve">311809350</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10036,15 +10036,15 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F201">
-        <v>1592</v>
+        <v>476</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809344</t>
+          <t xml:space="preserve">311809346</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10086,15 +10086,15 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F202">
-        <v>406</v>
+        <v>1592</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809345</t>
+          <t xml:space="preserve">311809344</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10136,15 +10136,15 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F203">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809353</t>
+          <t xml:space="preserve">311809345</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785197</t>
+          <t xml:space="preserve">5784905</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F204">
-        <v>460</v>
+        <v>302</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815182</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8227241</t>
+          <t xml:space="preserve">5785197</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10240,11 +10240,11 @@
         </is>
       </c>
       <c r="F205">
-        <v>343</v>
+        <v>460</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815183</t>
+          <t xml:space="preserve">311815182</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785311</t>
+          <t xml:space="preserve">8227241</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -10290,16 +10290,16 @@
         </is>
       </c>
       <c r="F206">
-        <v>1956</v>
+        <v>343</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821475</t>
+          <t xml:space="preserve">311815183</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-31</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287561</t>
+          <t xml:space="preserve">5785311</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10340,16 +10340,16 @@
         </is>
       </c>
       <c r="F207">
-        <v>3893</v>
+        <v>1956</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823018</t>
+          <t xml:space="preserve">311821475</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-05</t>
+          <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">10140604</t>
+          <t xml:space="preserve">5287561</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F208">
-        <v>690</v>
+        <v>3893</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838368</t>
+          <t xml:space="preserve">311823018</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-16</t>
+          <t xml:space="preserve">2035-04-05</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,20 +10431,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285296</t>
+          <t xml:space="preserve">10140604</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F209">
-        <v>313</v>
+        <v>690</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838372</t>
+          <t xml:space="preserve">311838368</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -10536,11 +10536,11 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -10581,20 +10581,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780820</t>
+          <t xml:space="preserve">5285296</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F212">
-        <v>1838</v>
+        <v>293</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838476</t>
+          <t xml:space="preserve">311838372</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10636,11 +10636,11 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F213">
-        <v>2577</v>
+        <v>1838</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5283387</t>
+          <t xml:space="preserve">5780820</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F214">
-        <v>1275</v>
+        <v>2577</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872709</t>
+          <t xml:space="preserve">311838476</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-10</t>
+          <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5293106</t>
+          <t xml:space="preserve">5283387</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -10740,16 +10740,16 @@
         </is>
       </c>
       <c r="F215">
-        <v>309</v>
+        <v>1275</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874211</t>
+          <t xml:space="preserve">311872709</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-10</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295339</t>
+          <t xml:space="preserve">5293106</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10790,11 +10790,11 @@
         </is>
       </c>
       <c r="F216">
-        <v>625</v>
+        <v>309</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874110</t>
+          <t xml:space="preserve">311874211</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295340</t>
+          <t xml:space="preserve">5295339</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10840,11 +10840,11 @@
         </is>
       </c>
       <c r="F217">
-        <v>664</v>
+        <v>625</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874111</t>
+          <t xml:space="preserve">311874110</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280052</t>
+          <t xml:space="preserve">5295340</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10890,16 +10890,16 @@
         </is>
       </c>
       <c r="F218">
-        <v>2377</v>
+        <v>664</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874111</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F219">
-        <v>648</v>
+        <v>2377</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783504</t>
+          <t xml:space="preserve">5280052</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F220">
-        <v>307</v>
+        <v>648</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874745</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-22</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,25 +11031,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955105</t>
+          <t xml:space="preserve">5783504</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F221">
-        <v>1284</v>
+        <v>307</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874954</t>
+          <t xml:space="preserve">311874745</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-29</t>
+          <t xml:space="preserve">2035-12-22</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786913</t>
+          <t xml:space="preserve">8955105</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F222">
-        <v>3416</v>
+        <v>1284</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880881</t>
+          <t xml:space="preserve">311874954</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-06</t>
+          <t xml:space="preserve">2035-12-29</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11136,15 +11136,15 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F223">
-        <v>1454</v>
+        <v>3416</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880883</t>
+          <t xml:space="preserve">311880881</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -11186,15 +11186,15 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F224">
-        <v>725</v>
+        <v>1454</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880886</t>
+          <t xml:space="preserve">311880883</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F225">
@@ -11286,11 +11286,11 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F226">
-        <v>501</v>
+        <v>725</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F227">
@@ -11381,20 +11381,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883339</t>
+          <t xml:space="preserve">5786913</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F228">
-        <v>758</v>
+        <v>501</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880882</t>
+          <t xml:space="preserve">311880886</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151675</t>
+          <t xml:space="preserve">9883339</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F229">
-        <v>282</v>
+        <v>758</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884427</t>
+          <t xml:space="preserve">311880882</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-26</t>
+          <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11486,15 +11486,15 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F230">
-        <v>729</v>
+        <v>282</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884430</t>
+          <t xml:space="preserve">311884427</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">308336, 308337</t>
+          <t xml:space="preserve">9151675</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F231">
-        <v>4431</v>
+        <v>729</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884501</t>
+          <t xml:space="preserve">311884428</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-27</t>
+          <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920169</t>
+          <t xml:space="preserve">311920155</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920169</t>
+          <t xml:space="preserve">311920155</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">

--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palævej 14</t>
+          <t xml:space="preserve">Aabenraavej 25A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100095648</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H2">
-        <v>294</v>
+        <v>2320</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingolf Nielsens Vej 21</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 100</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100341460</t>
+          <t xml:space="preserve">735652, 5292892</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H3">
-        <v>1978</v>
+        <v>2141</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingolf Nielsens Vej 17</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 100B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100341460</t>
+          <t xml:space="preserve">735659, 5292984</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>2870</v>
+        <v>280</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingolf Nielsens Vej 13B</t>
+          <t xml:space="preserve">Gammel Aabenraavej 22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100341460</t>
+          <t xml:space="preserve">5278661</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H5">
-        <v>5033</v>
+        <v>480</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,17 +331,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 1</t>
+          <t xml:space="preserve">Havnbjerg Center 15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100911120</t>
+          <t xml:space="preserve">5295391</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>384</v>
+        <v>1535</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringriderpladsen 5A</t>
+          <t xml:space="preserve">Havnen 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512217</t>
+          <t xml:space="preserve">5785626</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>318</v>
+        <v>1471</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørup Bygade 44A</t>
+          <t xml:space="preserve">Hesnæsvej 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">308336, 308337</t>
+          <t xml:space="preserve">735437, 5296576</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>4431</v>
+        <v>502</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 1</t>
+          <t xml:space="preserve">Hesnæsvej 4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">312395</t>
+          <t xml:space="preserve">5296575</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>3239</v>
+        <v>314</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundsmarkvej 74</t>
+          <t xml:space="preserve">Huholt 17A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">312396</t>
+          <t xml:space="preserve">735679, 100010060</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H10">
-        <v>4941</v>
+        <v>4873</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,17 +631,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 150</t>
+          <t xml:space="preserve">Høruphav Havn 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">735592, 9159262</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H11">
-        <v>6688</v>
+        <v>279</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 150A</t>
+          <t xml:space="preserve">Høruphav Havn 7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">312397</t>
+          <t xml:space="preserve">735453, 9159262</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H12">
-        <v>975</v>
+        <v>266</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 1</t>
+          <t xml:space="preserve">Industrivej 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">501384, 5781087, 501385</t>
+          <t xml:space="preserve">5286928</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>9658</v>
+        <v>1065</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraavej 25A</t>
+          <t xml:space="preserve">Industrivej 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">735313, 8953911</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>2320</v>
+        <v>1953</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 22</t>
+          <t xml:space="preserve">Ingolf Nielsens Vej 13B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278661</t>
+          <t xml:space="preserve">100341460</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H15">
-        <v>480</v>
+        <v>5033</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørretoft 8</t>
+          <t xml:space="preserve">Ingolf Nielsens Vej 17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281255</t>
+          <t xml:space="preserve">100341460</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H16">
-        <v>304</v>
+        <v>2870</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,17 +991,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 1</t>
+          <t xml:space="preserve">Ingolf Nielsens Vej 21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5286928</t>
+          <t xml:space="preserve">100341460</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>1065</v>
+        <v>1978</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langgade 22</t>
+          <t xml:space="preserve">Kystvej 15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287023</t>
+          <t xml:space="preserve">735395, 5258385</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnbjerg Center 15</t>
+          <t xml:space="preserve">Landevejen 2A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295391</t>
+          <t xml:space="preserve">735305, 5287162</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="H19">
-        <v>1535</v>
+        <v>317</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,17 +1171,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 60</t>
+          <t xml:space="preserve">Langgade 22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5296567</t>
+          <t xml:space="preserve">5287023</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="H20">
-        <v>823</v>
+        <v>329</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesnæsvej 4</t>
+          <t xml:space="preserve">Lysabildgade 4C</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5296575</t>
+          <t xml:space="preserve">735543, 5287561</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H21">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvej 19</t>
+          <t xml:space="preserve">Løngang 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298208</t>
+          <t xml:space="preserve">5781097</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>330</v>
+        <v>602</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løngang 2</t>
+          <t xml:space="preserve">Marina Allé 10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781097</t>
+          <t xml:space="preserve">9022305</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H23">
-        <v>602</v>
+        <v>430</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mølleparken 4</t>
+          <t xml:space="preserve">Mejerivej 13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781256</t>
+          <t xml:space="preserve">7870345</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>836</v>
+        <v>434</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringriderpladsen 9</t>
+          <t xml:space="preserve">Møllegade 60</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784885</t>
+          <t xml:space="preserve">5296567</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>602</v>
+        <v>823</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringriderpladsen 7</t>
+          <t xml:space="preserve">Mølleparken 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784885</t>
+          <t xml:space="preserve">5781256</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H26">
-        <v>738</v>
+        <v>836</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 2</t>
+          <t xml:space="preserve">Newtonsvej 1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785626</t>
+          <t xml:space="preserve">735763, 100093124</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H27">
-        <v>1471</v>
+        <v>421</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peblingestien 2</t>
+          <t xml:space="preserve">Nørrebro 1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">100911120</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>2778</v>
+        <v>384</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 2A</t>
+          <t xml:space="preserve">Nørretoft 8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">735305, 5287162</t>
+          <t xml:space="preserve">5281255</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H29">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 3</t>
+          <t xml:space="preserve">Palævej 14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">735313, 8953911</t>
+          <t xml:space="preserve">100095648</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H30">
-        <v>1953</v>
+        <v>294</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystvej 15</t>
+          <t xml:space="preserve">Peblingestien 2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">735395, 5258385</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H31">
-        <v>362</v>
+        <v>2778</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesnæsvej 2</t>
+          <t xml:space="preserve">Ringriderpladsen 5A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">735437, 5296576</t>
+          <t xml:space="preserve">1512217</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H32">
-        <v>502</v>
+        <v>318</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 18</t>
+          <t xml:space="preserve">Ringriderpladsen 7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">735450, 5280508</t>
+          <t xml:space="preserve">5784885</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H33">
-        <v>513</v>
+        <v>738</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høruphav Havn 7</t>
+          <t xml:space="preserve">Ringriderpladsen 9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">735453, 9159262</t>
+          <t xml:space="preserve">5784885</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>266</v>
+        <v>602</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysabildgade 4C</t>
+          <t xml:space="preserve">Sandvej 19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">735543, 5287561</t>
+          <t xml:space="preserve">5298208</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H35">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høruphav Havn 3</t>
+          <t xml:space="preserve">Skolevænget 18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">735592, 9159262</t>
+          <t xml:space="preserve">735450, 5280508</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>279</v>
+        <v>513</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verdens Ende 2</t>
+          <t xml:space="preserve">Strandvej 1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">735627, 9429184</t>
+          <t xml:space="preserve">501384, 5781087, 501385</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H37">
-        <v>536</v>
+        <v>9658</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verdens Ende 4</t>
+          <t xml:space="preserve">Sundgade 13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">735628, 9429184</t>
+          <t xml:space="preserve">735651, 5785510</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H38">
-        <v>534</v>
+        <v>656</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundgade 13</t>
+          <t xml:space="preserve">Tennis Alle 1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">735651, 5785510</t>
+          <t xml:space="preserve">735666, 5292071</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>656</v>
+        <v>2354</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 100</t>
+          <t xml:space="preserve">Verdens Ende 10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">735652, 5292892</t>
+          <t xml:space="preserve">735654, 9429184</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H40">
-        <v>2141</v>
+        <v>298</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verdens Ende 10</t>
+          <t xml:space="preserve">Verdens Ende 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">735654, 9429184</t>
+          <t xml:space="preserve">735627, 9429184</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H41">
-        <v>298</v>
+        <v>536</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 100B</t>
+          <t xml:space="preserve">Verdens Ende 4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">735659, 5292984</t>
+          <t xml:space="preserve">735628, 9429184</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H42">
-        <v>280</v>
+        <v>534</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,17 +2551,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennis Alle 1</t>
+          <t xml:space="preserve">Løjtertoft 7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">735666, 5292071</t>
+          <t xml:space="preserve">5787622</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="H43">
-        <v>2354</v>
+        <v>1001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200009991</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-01-15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2611,40 +2611,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huholt 17A</t>
+          <t xml:space="preserve">Flintholmvej 4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">735679, 100010060</t>
+          <t xml:space="preserve">5787788</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>4873</v>
+        <v>1857</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010534</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-09</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2671,40 +2671,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newtonsvej 1</t>
+          <t xml:space="preserve">Storegade 14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">735763, 100093124</t>
+          <t xml:space="preserve">5785700</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010697</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2731,40 +2731,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 13</t>
+          <t xml:space="preserve">Tangsmose 2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870345</t>
+          <t xml:space="preserve">5285761</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>434</v>
+        <v>364</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011492</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,40 +2791,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marina Allé 10</t>
+          <t xml:space="preserve">Bonderosevej 1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022305</t>
+          <t xml:space="preserve">5285444</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>430</v>
+        <v>1217</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011536</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-17</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjtertoft 7</t>
+          <t xml:space="preserve">Kærvej 17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787622</t>
+          <t xml:space="preserve">5783138</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="H48">
-        <v>1001</v>
+        <v>1072</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009991</t>
+          <t xml:space="preserve">200011633</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-01-15</t>
+          <t xml:space="preserve">2019-03-18</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholmvej 4</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787788</t>
+          <t xml:space="preserve">5295266</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,16 +2930,16 @@
         </is>
       </c>
       <c r="H49">
-        <v>1857</v>
+        <v>9679</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010534</t>
+          <t xml:space="preserve">200012359</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-09</t>
+          <t xml:space="preserve">2019-04-07</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 14</t>
+          <t xml:space="preserve">B.S.Ingemanns Vej 3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785700</t>
+          <t xml:space="preserve">7967180</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>336</v>
+        <v>1682</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010697</t>
+          <t xml:space="preserve">200012502</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-17</t>
+          <t xml:space="preserve">2019-04-15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangsmose 2</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 100A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285761</t>
+          <t xml:space="preserve">5292892</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>364</v>
+        <v>905</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011492</t>
+          <t xml:space="preserve">200012601</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-16</t>
+          <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bonderosevej 1</t>
+          <t xml:space="preserve">Rådyrvej 1A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285444</t>
+          <t xml:space="preserve">9665069</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>1217</v>
+        <v>686</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011536</t>
+          <t xml:space="preserve">200012921</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-17</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 17</t>
+          <t xml:space="preserve">Kongevej 35</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783138</t>
+          <t xml:space="preserve">1512218</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>1072</v>
+        <v>6492</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011633</t>
+          <t xml:space="preserve">200014764</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-18</t>
+          <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Stjernevej 63</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295266</t>
+          <t xml:space="preserve">5259087</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>9679</v>
+        <v>735</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012359</t>
+          <t xml:space="preserve">200016722</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-07</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S.Ingemanns Vej 3</t>
+          <t xml:space="preserve">Buskmosevej 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967180</t>
+          <t xml:space="preserve">5272978</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="H55">
-        <v>1682</v>
+        <v>499</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012502</t>
+          <t xml:space="preserve">200017325</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-15</t>
+          <t xml:space="preserve">2019-07-09</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 100A</t>
+          <t xml:space="preserve">Bækvej 10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292892</t>
+          <t xml:space="preserve">9151738</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>905</v>
+        <v>362</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012601</t>
+          <t xml:space="preserve">100127221</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-17</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådyrvej 1A</t>
+          <t xml:space="preserve">Løkkegårdsvej 3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665069</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H57">
-        <v>686</v>
+        <v>310</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012921</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 35</t>
+          <t xml:space="preserve">Skydebanevej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512218</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H58">
-        <v>6492</v>
+        <v>996</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014764</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-10</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stjernevej 63</t>
+          <t xml:space="preserve">Skydebanevej 4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259087</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H59">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016722</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buskmosevej 2</t>
+          <t xml:space="preserve">Under Broen 20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272978</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>499</v>
+        <v>340</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017325</t>
+          <t xml:space="preserve">200018087</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-09</t>
+          <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 10</t>
+          <t xml:space="preserve">Skydebanevej 4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151738</t>
+          <t xml:space="preserve">9022162</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H61">
-        <v>362</v>
+        <v>529</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100127221</t>
+          <t xml:space="preserve">200018102</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under Broen 20</t>
+          <t xml:space="preserve">Færgevej 68</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>340</v>
+        <v>573</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018087</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-30</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 4</t>
+          <t xml:space="preserve">Færgevej 70</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5297522</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>752</v>
+        <v>274</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018087</t>
+          <t xml:space="preserve">200019220</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-30</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 1</t>
+          <t xml:space="preserve">Mågevænget 10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5292814</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>996</v>
+        <v>4679</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018087</t>
+          <t xml:space="preserve">200023568</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-30</t>
+          <t xml:space="preserve">2019-11-08</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løkkegårdsvej 3</t>
+          <t xml:space="preserve">Søvænget 7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5787053</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018087</t>
+          <t xml:space="preserve">200023607</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-30</t>
+          <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 4</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022162</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H66">
-        <v>529</v>
+        <v>4233</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018102</t>
+          <t xml:space="preserve">200023653</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,35 +3991,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 70</t>
+          <t xml:space="preserve">Lille Rådhusgade 10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">8111599</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H67">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200023651</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 68</t>
+          <t xml:space="preserve">Avntoftvej 8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5297522</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H68">
-        <v>573</v>
+        <v>1717</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019220</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mågevænget 10</t>
+          <t xml:space="preserve">Avntoftvej 8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292814</t>
+          <t xml:space="preserve">735399, 5271415</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H69">
-        <v>4679</v>
+        <v>624</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023568</t>
+          <t xml:space="preserve">200025499</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-08</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvænget 7</t>
+          <t xml:space="preserve">Kegnæsvej 12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787053</t>
+          <t xml:space="preserve">5287570</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>361</v>
+        <v>287</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023607</t>
+          <t xml:space="preserve">200029910</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-09</t>
+          <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20</t>
+          <t xml:space="preserve">Ulbjerggade 29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">5787473</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>4233</v>
+        <v>296</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023653</t>
+          <t xml:space="preserve">200029940</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Rådhusgade 10</t>
+          <t xml:space="preserve">Mejerivej 13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8111599</t>
+          <t xml:space="preserve">7870345</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H72">
-        <v>329</v>
+        <v>579</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023651</t>
+          <t xml:space="preserve">200030269</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2020-04-13</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avntoftvej 8</t>
+          <t xml:space="preserve">A D Jørgensensgade 12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">5258778</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>1717</v>
+        <v>525</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025499</t>
+          <t xml:space="preserve">200031045</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avntoftvej 8</t>
+          <t xml:space="preserve">Aabenraavej 25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">735399, 5271415</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H74">
-        <v>624</v>
+        <v>4816</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025499</t>
+          <t xml:space="preserve">310000776</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2022-06-27</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kegnæsvej 12</t>
+          <t xml:space="preserve">Møllegade 54</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287570</t>
+          <t xml:space="preserve">8166350</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H75">
-        <v>287</v>
+        <v>1494</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029910</t>
+          <t xml:space="preserve">311041979</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-31</t>
+          <t xml:space="preserve">2024-03-10</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulbjerggade 29</t>
+          <t xml:space="preserve">Svanehaven 2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787473</t>
+          <t xml:space="preserve">100019921</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>296</v>
+        <v>7293</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029940</t>
+          <t xml:space="preserve">311086987</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-31</t>
+          <t xml:space="preserve">2024-12-08</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,45 +4591,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 13</t>
+          <t xml:space="preserve">Nørre Havnegade 15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870345</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>579</v>
+        <v>1276</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030269</t>
+          <t xml:space="preserve">311301220</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-13</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4651,45 +4651,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">A D Jørgensensgade 12</t>
+          <t xml:space="preserve">Nørre Havnegade 15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5258778</t>
+          <t xml:space="preserve">5780656</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>525</v>
+        <v>4367</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031045</t>
+          <t xml:space="preserve">311301223</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-04</t>
+          <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraavej 25</t>
+          <t xml:space="preserve">Præstegårdsvej 8A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,35 +4721,35 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">10185368</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>4816</v>
+        <v>984</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000776</t>
+          <t xml:space="preserve">311370738</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-27</t>
+          <t xml:space="preserve">2029-04-11</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 54</t>
+          <t xml:space="preserve">Avnbølvej 12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,35 +4781,35 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8166350</t>
+          <t xml:space="preserve">9072481</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>1494</v>
+        <v>290</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041979</t>
+          <t xml:space="preserve">311373248</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-10</t>
+          <t xml:space="preserve">2029-04-26</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanehaven 2</t>
+          <t xml:space="preserve">Kærvej 70</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019921</t>
+          <t xml:space="preserve">5783317</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="H81">
-        <v>7293</v>
+        <v>1702</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086987</t>
+          <t xml:space="preserve">311436294</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-08</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Havnegade 15</t>
+          <t xml:space="preserve">Kær Bygade 19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">8917210</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>1276</v>
+        <v>1325</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301220</t>
+          <t xml:space="preserve">311495939</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Havnegade 15</t>
+          <t xml:space="preserve">Nørregade 11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780656</t>
+          <t xml:space="preserve">8583585</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>4367</v>
+        <v>522</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301223</t>
+          <t xml:space="preserve">311498594</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-06</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 8A</t>
+          <t xml:space="preserve">Stråbjergvej 1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,25 +5021,25 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10185368</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H84">
-        <v>984</v>
+        <v>6889</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311370738</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-11</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avnbølvej 12</t>
+          <t xml:space="preserve">Stråbjergvej 1A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072481</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H85">
-        <v>290</v>
+        <v>1468</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373248</t>
+          <t xml:space="preserve">311521352</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-26</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 70</t>
+          <t xml:space="preserve">Stråbjergvej 3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783317</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>1702</v>
+        <v>10229</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436294</t>
+          <t xml:space="preserve">311521350</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-06</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kær Bygade 19</t>
+          <t xml:space="preserve">Stråbjergvej 7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,25 +5201,25 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917210</t>
+          <t xml:space="preserve">9022286</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H87">
-        <v>1325</v>
+        <v>1157</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495939</t>
+          <t xml:space="preserve">311521353</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11</t>
+          <t xml:space="preserve">Skolevej 19A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8583585</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>522</v>
+        <v>261</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498594</t>
+          <t xml:space="preserve">311560181</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 3</t>
+          <t xml:space="preserve">Skolevej 19B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H89">
-        <v>10229</v>
+        <v>689</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521350</t>
+          <t xml:space="preserve">311560185</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 1</t>
+          <t xml:space="preserve">Skolevej 21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>6889</v>
+        <v>402</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311560182</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 1A</t>
+          <t xml:space="preserve">Skolevej 21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H91">
-        <v>1468</v>
+        <v>5032</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521352</t>
+          <t xml:space="preserve">311560184</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stråbjergvej 7</t>
+          <t xml:space="preserve">Skolevej 21B</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,25 +5501,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022286</t>
+          <t xml:space="preserve">5281219</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H92">
-        <v>1157</v>
+        <v>560</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521353</t>
+          <t xml:space="preserve">311560186</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-19</t>
+          <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 23B</t>
+          <t xml:space="preserve">Skolevej 21D</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5566,15 +5566,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H93">
-        <v>1583</v>
+        <v>1198</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19A</t>
+          <t xml:space="preserve">Skolevej 23B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5686,15 +5686,15 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>261</v>
+        <v>1583</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19B</t>
+          <t xml:space="preserve">B.S.Ingemanns Vej 1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H96">
-        <v>689</v>
+        <v>1740</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560982</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21D</t>
+          <t xml:space="preserve">Engelshøjgade 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">8175481</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>1198</v>
+        <v>776</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560963</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21</t>
+          <t xml:space="preserve">Grundtvigs Alle 100</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="H98">
-        <v>402</v>
+        <v>9839</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21</t>
+          <t xml:space="preserve">Grundtvigs Alle 100A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,25 +5921,25 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">5784816</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H99">
-        <v>5032</v>
+        <v>487</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560980</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 21B</t>
+          <t xml:space="preserve">Vestervej 42</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281219</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>560</v>
+        <v>10333</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560186</t>
+          <t xml:space="preserve">311568970</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S.Ingemanns Vej 1</t>
+          <t xml:space="preserve">Vestervej 42B</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>1740</v>
+        <v>3913</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560982</t>
+          <t xml:space="preserve">311568975</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 100</t>
+          <t xml:space="preserve">Vestervej 42D</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">1808468</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H102">
-        <v>9839</v>
+        <v>500</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311568971</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigs Alle 100A</t>
+          <t xml:space="preserve">Primulavej 2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784816</t>
+          <t xml:space="preserve">5786366</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>487</v>
+        <v>355</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560980</t>
+          <t xml:space="preserve">311652254</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelshøjgade 1</t>
+          <t xml:space="preserve">Grundtvigs Alle 150</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,25 +6221,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8175481</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H104">
-        <v>776</v>
+        <v>6688</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560963</t>
+          <t xml:space="preserve">311661617</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,35 +6271,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42</t>
+          <t xml:space="preserve">Grundtvigs Alle 150A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">312397</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H105">
-        <v>10333</v>
+        <v>975</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568970</t>
+          <t xml:space="preserve">311661616</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42B</t>
+          <t xml:space="preserve">Kløvermarken 1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">312395</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>3913</v>
+        <v>3239</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568975</t>
+          <t xml:space="preserve">311661619</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 42D</t>
+          <t xml:space="preserve">Sundsmarkvej 74</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808468</t>
+          <t xml:space="preserve">312396</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H107">
-        <v>500</v>
+        <v>4941</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568971</t>
+          <t xml:space="preserve">311661618</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primulavej 2</t>
+          <t xml:space="preserve">Gyden 96</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786366</t>
+          <t xml:space="preserve">5290028</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>355</v>
+        <v>3620</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652254</t>
+          <t xml:space="preserve">311674038</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6526,15 +6526,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H109">
-        <v>3620</v>
+        <v>1433</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674038</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674038</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyden 96</t>
+          <t xml:space="preserve">Kaplenivej 3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290028</t>
+          <t xml:space="preserve">9022207</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>1433</v>
+        <v>5131</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674521</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6706,11 +6706,11 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H112">
-        <v>5131</v>
+        <v>5091</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6766,11 +6766,11 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H113">
-        <v>5091</v>
+        <v>775</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaplenivej 3</t>
+          <t xml:space="preserve">Vestergade 17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022207</t>
+          <t xml:space="preserve">5275405</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>775</v>
+        <v>1266</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674521</t>
+          <t xml:space="preserve">311675319</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-18</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6886,11 +6886,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H115">
-        <v>1266</v>
+        <v>1041</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6946,11 +6946,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H116">
-        <v>1041</v>
+        <v>831</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7006,11 +7006,11 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H117">
-        <v>831</v>
+        <v>1054</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7066,11 +7066,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H118">
-        <v>1054</v>
+        <v>2025</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7126,11 +7126,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H119">
-        <v>2025</v>
+        <v>331</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H120">
-        <v>331</v>
+        <v>684</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 17</t>
+          <t xml:space="preserve">Nejsvej 19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,25 +7241,25 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275405</t>
+          <t xml:space="preserve">5276459</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H121">
-        <v>684</v>
+        <v>1833</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675319</t>
+          <t xml:space="preserve">311677211</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7306,11 +7306,11 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H122">
-        <v>1833</v>
+        <v>1297</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 19</t>
+          <t xml:space="preserve">Nejsvej 19A</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7366,20 +7366,20 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H123">
-        <v>1297</v>
+        <v>702</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677211</t>
+          <t xml:space="preserve">311677608</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-28</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejsvej 19A</t>
+          <t xml:space="preserve">Kettingvej 1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5276459</t>
+          <t xml:space="preserve">8954042</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>702</v>
+        <v>1345</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677608</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7546,15 +7546,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H126">
-        <v>1345</v>
+        <v>725</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1D</t>
+          <t xml:space="preserve">Kettingvej 1C</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7666,15 +7666,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="H128">
-        <v>1707</v>
+        <v>462</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686707</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1C</t>
+          <t xml:space="preserve">Kettingvej 1D</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7726,15 +7726,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H129">
-        <v>462</v>
+        <v>1707</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686707</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1F</t>
+          <t xml:space="preserve">Kettingvej 1E</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7786,11 +7786,11 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H130">
-        <v>2353</v>
+        <v>1906</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1E</t>
+          <t xml:space="preserve">Kettingvej 1F</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7846,11 +7846,11 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="H131">
-        <v>1906</v>
+        <v>2353</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 8</t>
+          <t xml:space="preserve">Kettingvej 1F</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7906,15 +7906,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H132">
-        <v>390</v>
+        <v>1691</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686708</t>
+          <t xml:space="preserve">311686706</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1F</t>
+          <t xml:space="preserve">Stadionvej 8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7966,15 +7966,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H133">
-        <v>1691</v>
+        <v>390</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311686708</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8011,35 +8011,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 1</t>
+          <t xml:space="preserve">Arnkilgade 74</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8954042</t>
+          <t xml:space="preserve">5292219</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H134">
-        <v>725</v>
+        <v>1110</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686706</t>
+          <t xml:space="preserve">311690728</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-09</t>
+          <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8086,15 +8086,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H135">
-        <v>1110</v>
+        <v>1045</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690728</t>
+          <t xml:space="preserve">311690729</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnkilgade 74</t>
+          <t xml:space="preserve">Kystvej 1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5292219</t>
+          <t xml:space="preserve">5257652</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H136">
-        <v>1045</v>
+        <v>531</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690729</t>
+          <t xml:space="preserve">311692727</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-26</t>
+          <t xml:space="preserve">2033-07-04</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8206,20 +8206,20 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>531</v>
+        <v>6400</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692727</t>
+          <t xml:space="preserve">311693153</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-04</t>
+          <t xml:space="preserve">2033-07-05</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystvej 1</t>
+          <t xml:space="preserve">Degnevænget 2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257652</t>
+          <t xml:space="preserve">5257645</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,16 +8270,16 @@
         </is>
       </c>
       <c r="H138">
-        <v>6400</v>
+        <v>2539</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311693153</t>
+          <t xml:space="preserve">311696049</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-05</t>
+          <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8326,11 +8326,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H139">
-        <v>2539</v>
+        <v>1312</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8386,20 +8386,20 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H140">
-        <v>1312</v>
+        <v>1233</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696049</t>
+          <t xml:space="preserve">311696243</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-20</t>
+          <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2</t>
+          <t xml:space="preserve">Degnevænget 2E</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8446,15 +8446,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H141">
-        <v>1233</v>
+        <v>1981</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696243</t>
+          <t xml:space="preserve">311696280</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2E</t>
+          <t xml:space="preserve">Degnevænget 2C</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8566,20 +8566,20 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H143">
-        <v>1981</v>
+        <v>501</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696280</t>
+          <t xml:space="preserve">311696375</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-21</t>
+          <t xml:space="preserve">2033-07-24</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 2C</t>
+          <t xml:space="preserve">Johs Kochsvej 12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8626,20 +8626,20 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H144">
-        <v>501</v>
+        <v>252</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696375</t>
+          <t xml:space="preserve">311697270</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-24</t>
+          <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johs Kochsvej 12</t>
+          <t xml:space="preserve">Gammel Aabenraavej 24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257645</t>
+          <t xml:space="preserve">5784337</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H146">
-        <v>252</v>
+        <v>5859</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697270</t>
+          <t xml:space="preserve">311698797</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-31</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 24</t>
+          <t xml:space="preserve">Skovvej 2A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,25 +8801,25 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784337</t>
+          <t xml:space="preserve">5782338</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H147">
-        <v>5859</v>
+        <v>5091</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698797</t>
+          <t xml:space="preserve">311717581</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8866,15 +8866,15 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H148">
-        <v>5091</v>
+        <v>800</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717580</t>
+          <t xml:space="preserve">311717585</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 2A</t>
+          <t xml:space="preserve">Skovvej 4</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,20 +8921,20 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5782338</t>
+          <t xml:space="preserve">7181513</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H149">
-        <v>800</v>
+        <v>267</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717580</t>
+          <t xml:space="preserve">311717579</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 4</t>
+          <t xml:space="preserve">Ahlefeldvej 4</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7181513</t>
+          <t xml:space="preserve">5257481</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>267</v>
+        <v>4554</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717579</t>
+          <t xml:space="preserve">311758410</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9046,11 +9046,11 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H151">
-        <v>4554</v>
+        <v>397</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -9091,30 +9091,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldvej 4</t>
+          <t xml:space="preserve">Allegade 4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5257481</t>
+          <t xml:space="preserve">5275746</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>397</v>
+        <v>1497</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758410</t>
+          <t xml:space="preserve">311758407</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 4</t>
+          <t xml:space="preserve">Flintevænget 67</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275746</t>
+          <t xml:space="preserve">5294810</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,16 +9170,16 @@
         </is>
       </c>
       <c r="H153">
-        <v>1497</v>
+        <v>570</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758407</t>
+          <t xml:space="preserve">311761633</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintevænget 67</t>
+          <t xml:space="preserve">Nørreled 31</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294810</t>
+          <t xml:space="preserve">7846650</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9290,11 +9290,11 @@
         </is>
       </c>
       <c r="H155">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761633</t>
+          <t xml:space="preserve">311761632</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9346,11 +9346,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H156">
-        <v>597</v>
+        <v>1220</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9391,35 +9391,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreled 31</t>
+          <t xml:space="preserve">Bakkensbro 6</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7846650</t>
+          <t xml:space="preserve">5281873</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H157">
-        <v>1220</v>
+        <v>1305</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761632</t>
+          <t xml:space="preserve">311762260</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-24</t>
+          <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9466,11 +9466,11 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H158">
-        <v>1305</v>
+        <v>429</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkensbro 6</t>
+          <t xml:space="preserve">Bakkensbro 8</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9526,11 +9526,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H159">
-        <v>429</v>
+        <v>592</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -9571,30 +9571,30 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkensbro 8</t>
+          <t xml:space="preserve">Hølle Vej 4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5281873</t>
+          <t xml:space="preserve">8955245</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>592</v>
+        <v>1449</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762260</t>
+          <t xml:space="preserve">311762253</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9691,35 +9691,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hølle Vej 4</t>
+          <t xml:space="preserve">Skolegade 21</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955245</t>
+          <t xml:space="preserve">5294181</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H162">
-        <v>1449</v>
+        <v>2590</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762253</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9766,11 +9766,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H163">
-        <v>2590</v>
+        <v>606</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 9</t>
+          <t xml:space="preserve">Skolegade 23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9826,15 +9826,15 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H164">
-        <v>329</v>
+        <v>4077</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766886</t>
+          <t xml:space="preserve">311766889</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9886,15 +9886,15 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H165">
-        <v>4077</v>
+        <v>1160</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311766887</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 23</t>
+          <t xml:space="preserve">Skolegade 9</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9946,15 +9946,15 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H166">
-        <v>1160</v>
+        <v>329</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766887</t>
+          <t xml:space="preserve">311766886</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 21</t>
+          <t xml:space="preserve">Luffes Plads 2</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,25 +10001,25 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294181</t>
+          <t xml:space="preserve">9562993</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H167">
-        <v>606</v>
+        <v>1425</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766889</t>
+          <t xml:space="preserve">311771819</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,35 +10051,35 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luffes Plads 2</t>
+          <t xml:space="preserve">Dalsmark 13</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562993</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>1425</v>
+        <v>2404</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771819</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-05</t>
+          <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 10</t>
+          <t xml:space="preserve">Dalsmark 13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,20 +10121,20 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272155</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H169">
-        <v>1794</v>
+        <v>676</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788055</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 10C</t>
+          <t xml:space="preserve">Dalsmark 13</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272155</t>
+          <t xml:space="preserve">5273073</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H170">
-        <v>779</v>
+        <v>690</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788056</t>
+          <t xml:space="preserve">311788050</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenvej 28</t>
+          <t xml:space="preserve">Højløkke 2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5272862</t>
+          <t xml:space="preserve">8515752</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10250,11 +10250,11 @@
         </is>
       </c>
       <c r="H171">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788048</t>
+          <t xml:space="preserve">311788047</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsmark 13</t>
+          <t xml:space="preserve">Stenvej 10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">5272155</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10310,11 +10310,11 @@
         </is>
       </c>
       <c r="H172">
-        <v>2404</v>
+        <v>1794</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788055</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsmark 13</t>
+          <t xml:space="preserve">Stenvej 10C</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">5272155</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10370,11 +10370,11 @@
         </is>
       </c>
       <c r="H173">
-        <v>676</v>
+        <v>779</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788056</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsmark 13</t>
+          <t xml:space="preserve">Stenvej 28</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10421,20 +10421,20 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5273073</t>
+          <t xml:space="preserve">5272862</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>690</v>
+        <v>533</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788050</t>
+          <t xml:space="preserve">311788048</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10471,35 +10471,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højløkke 2</t>
+          <t xml:space="preserve">Luffes Plads 4</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8515752</t>
+          <t xml:space="preserve">5787099</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H175">
-        <v>532</v>
+        <v>266</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788047</t>
+          <t xml:space="preserve">311797325</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-27</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luffes Plads 4</t>
+          <t xml:space="preserve">Industrivej 5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787099</t>
+          <t xml:space="preserve">5278117</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>266</v>
+        <v>745</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797325</t>
+          <t xml:space="preserve">311799237</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-11-25</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,35 +10831,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 5</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20B</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278117</t>
+          <t xml:space="preserve">5278178</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H181">
-        <v>745</v>
+        <v>609</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311799237</t>
+          <t xml:space="preserve">311800215</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-25</t>
+          <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20B</t>
+          <t xml:space="preserve">Gammel Aabenraavej 20E</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10966,15 +10966,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H183">
-        <v>609</v>
+        <v>2605</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800215</t>
+          <t xml:space="preserve">311800217</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Aabenraavej 20E</t>
+          <t xml:space="preserve">Dybbølsten 29</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,25 +11021,25 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278178</t>
+          <t xml:space="preserve">5279082</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>2605</v>
+        <v>382</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800217</t>
+          <t xml:space="preserve">311803358</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-29</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 19</t>
+          <t xml:space="preserve">Gammeldam 2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1512200</t>
+          <t xml:space="preserve">8940680</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11090,11 +11090,11 @@
         </is>
       </c>
       <c r="H185">
-        <v>2901</v>
+        <v>485</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803350</t>
+          <t xml:space="preserve">311803387</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palmose 14</t>
+          <t xml:space="preserve">Kirke Alle 9</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5278572</t>
+          <t xml:space="preserve">5781025</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11150,11 +11150,11 @@
         </is>
       </c>
       <c r="H186">
-        <v>917</v>
+        <v>1339</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805471</t>
+          <t xml:space="preserve">311803378</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dybbølsten 29</t>
+          <t xml:space="preserve">Kirke Alle 9A</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,20 +11201,20 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5279082</t>
+          <t xml:space="preserve">5781025</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H187">
-        <v>382</v>
+        <v>317</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803358</t>
+          <t xml:space="preserve">311803381</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 9</t>
+          <t xml:space="preserve">Kongevej 19</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781025</t>
+          <t xml:space="preserve">1512200</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11270,11 +11270,11 @@
         </is>
       </c>
       <c r="H188">
-        <v>1339</v>
+        <v>2901</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803378</t>
+          <t xml:space="preserve">311803350</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11311,30 +11311,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 9A</t>
+          <t xml:space="preserve">Løjtertoft 32</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781025</t>
+          <t xml:space="preserve">5787147</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H189">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803381</t>
+          <t xml:space="preserve">311803395</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,17 +11371,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Nyrops Plads 2</t>
+          <t xml:space="preserve">Mads Clausens Vej 103</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5781423</t>
+          <t xml:space="preserve">8995417</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>1859</v>
+        <v>604</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803364</t>
+          <t xml:space="preserve">311803386</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjtertoft 32</t>
+          <t xml:space="preserve">Mads Clausens Vej 13</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787147</t>
+          <t xml:space="preserve">5787761</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11450,11 +11450,11 @@
         </is>
       </c>
       <c r="H191">
-        <v>385</v>
+        <v>4402</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803395</t>
+          <t xml:space="preserve">311803385</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,17 +11491,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 13</t>
+          <t xml:space="preserve">Martin Nyrops Plads 2</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787761</t>
+          <t xml:space="preserve">5781423</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11510,11 +11510,11 @@
         </is>
       </c>
       <c r="H192">
-        <v>4402</v>
+        <v>1859</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803385</t>
+          <t xml:space="preserve">311803364</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11551,17 +11551,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammeldam 2</t>
+          <t xml:space="preserve">Palmose 14</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940680</t>
+          <t xml:space="preserve">5278572</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,11 +11570,11 @@
         </is>
       </c>
       <c r="H193">
-        <v>485</v>
+        <v>917</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803387</t>
+          <t xml:space="preserve">311803369</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11611,17 +11611,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 103</t>
+          <t xml:space="preserve">Drosselvænget 1</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995417</t>
+          <t xml:space="preserve">5275696</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11630,16 +11630,16 @@
         </is>
       </c>
       <c r="H194">
-        <v>604</v>
+        <v>385</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803386</t>
+          <t xml:space="preserve">311803590</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,17 +11671,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvænget 1</t>
+          <t xml:space="preserve">Mellemvej 16</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5275696</t>
+          <t xml:space="preserve">5787784</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11690,11 +11690,11 @@
         </is>
       </c>
       <c r="H195">
-        <v>385</v>
+        <v>868</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803590</t>
+          <t xml:space="preserve">311803725</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvej 16</t>
+          <t xml:space="preserve">Stavensbølgade 66</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6440</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787784</t>
+          <t xml:space="preserve">5286834</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11810,16 +11810,16 @@
         </is>
       </c>
       <c r="H197">
-        <v>868</v>
+        <v>365</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803725</t>
+          <t xml:space="preserve">311809080</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-19</t>
+          <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,35 +11851,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavensbølgade 66</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26B</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5286834</t>
+          <t xml:space="preserve">5784905</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H198">
-        <v>365</v>
+        <v>1592</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809080</t>
+          <t xml:space="preserve">311809344</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26E</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26C</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H199">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809348</t>
+          <t xml:space="preserve">311809346</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26C</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26E</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H201">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809346</t>
+          <t xml:space="preserve">311809348</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26B</t>
+          <t xml:space="preserve">Borgmester Andersens Vej 26G</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12106,15 +12106,15 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H202">
-        <v>1592</v>
+        <v>302</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809344</t>
+          <t xml:space="preserve">311809353</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Andersens Vej 26G</t>
+          <t xml:space="preserve">Friheds Alle 45A</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12221,25 +12221,25 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5784905</t>
+          <t xml:space="preserve">5785197</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H204">
-        <v>302</v>
+        <v>460</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809351</t>
+          <t xml:space="preserve">311815182</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-03</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12271,17 +12271,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Friheds Alle 45A</t>
+          <t xml:space="preserve">Kløverlykke 31</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785197</t>
+          <t xml:space="preserve">8227241</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -12290,11 +12290,11 @@
         </is>
       </c>
       <c r="H205">
-        <v>460</v>
+        <v>343</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815182</t>
+          <t xml:space="preserve">311815183</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12331,17 +12331,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløverlykke 31</t>
+          <t xml:space="preserve">Skovvej 16</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8227241</t>
+          <t xml:space="preserve">5785311</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,16 +12350,16 @@
         </is>
       </c>
       <c r="H206">
-        <v>343</v>
+        <v>1956</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815183</t>
+          <t xml:space="preserve">311821475</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,17 +12391,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 16</t>
+          <t xml:space="preserve">Lysabildgade 2</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5785311</t>
+          <t xml:space="preserve">5287561</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -12410,16 +12410,16 @@
         </is>
       </c>
       <c r="H207">
-        <v>1956</v>
+        <v>3893</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821475</t>
+          <t xml:space="preserve">311823018</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-31</t>
+          <t xml:space="preserve">2035-04-05</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysabildgade 2</t>
+          <t xml:space="preserve">Knøs' Gård 1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5287561</t>
+          <t xml:space="preserve">5285296</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,16 +12470,16 @@
         </is>
       </c>
       <c r="H208">
-        <v>3893</v>
+        <v>313</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823018</t>
+          <t xml:space="preserve">311838372</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-05</t>
+          <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,30 +12511,30 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkgade 54</t>
+          <t xml:space="preserve">Knøs' Gård 1</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">10140604</t>
+          <t xml:space="preserve">5285296</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H209">
-        <v>690</v>
+        <v>298</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838368</t>
+          <t xml:space="preserve">311838372</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12586,11 +12586,11 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H210">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -12631,30 +12631,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knøs' Gård 1</t>
+          <t xml:space="preserve">Lille Rådhusgade 7</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285296</t>
+          <t xml:space="preserve">5780820</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H211">
-        <v>298</v>
+        <v>1838</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838372</t>
+          <t xml:space="preserve">311838476</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12691,30 +12691,30 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knøs' Gård 1</t>
+          <t xml:space="preserve">Parkgade 54</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5285296</t>
+          <t xml:space="preserve">10140604</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H212">
-        <v>293</v>
+        <v>690</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838372</t>
+          <t xml:space="preserve">311838368</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Rådhusgade 7</t>
+          <t xml:space="preserve">Vothmanns Plads 2</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12766,11 +12766,11 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H213">
-        <v>1838</v>
+        <v>2577</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -12811,35 +12811,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vothmanns Plads 2</t>
+          <t xml:space="preserve">Sundgade 100</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780820</t>
+          <t xml:space="preserve">5283387</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H214">
-        <v>2577</v>
+        <v>1275</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838476</t>
+          <t xml:space="preserve">311872709</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-16</t>
+          <t xml:space="preserve">2035-12-10</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12871,17 +12871,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundgade 100</t>
+          <t xml:space="preserve">Huholt 13</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5283387</t>
+          <t xml:space="preserve">5293106</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12890,16 +12890,16 @@
         </is>
       </c>
       <c r="H215">
-        <v>1275</v>
+        <v>309</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872709</t>
+          <t xml:space="preserve">311874211</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-10</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12931,17 +12931,17 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huholt 13</t>
+          <t xml:space="preserve">Piledamsvej 4</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5293106</t>
+          <t xml:space="preserve">5295339</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12950,11 +12950,11 @@
         </is>
       </c>
       <c r="H216">
-        <v>309</v>
+        <v>625</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874211</t>
+          <t xml:space="preserve">311874110</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledamsvej 4</t>
+          <t xml:space="preserve">Piledamsvej 4C</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295339</t>
+          <t xml:space="preserve">5295340</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -13010,11 +13010,11 @@
         </is>
       </c>
       <c r="H217">
-        <v>625</v>
+        <v>664</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874110</t>
+          <t xml:space="preserve">311874111</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledamsvej 4C</t>
+          <t xml:space="preserve">Katforte 20</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295340</t>
+          <t xml:space="preserve">5280052</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -13070,16 +13070,16 @@
         </is>
       </c>
       <c r="H218">
-        <v>664</v>
+        <v>2377</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874111</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13126,11 +13126,11 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H219">
-        <v>2377</v>
+        <v>648</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katforte 20</t>
+          <t xml:space="preserve">Sundsmarkvej 72</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280052</t>
+          <t xml:space="preserve">5783504</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H220">
-        <v>648</v>
+        <v>307</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874745</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2035-12-22</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13231,35 +13231,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundsmarkvej 72</t>
+          <t xml:space="preserve">Illerstrandvej 7</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5783504</t>
+          <t xml:space="preserve">8955105</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H221">
-        <v>307</v>
+        <v>1284</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874745</t>
+          <t xml:space="preserve">311874954</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-22</t>
+          <t xml:space="preserve">2035-12-29</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13291,35 +13291,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Illerstrandvej 7</t>
+          <t xml:space="preserve">Tangshave 1</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6430</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8955105</t>
+          <t xml:space="preserve">5786913</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H222">
-        <v>1284</v>
+        <v>3416</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874954</t>
+          <t xml:space="preserve">311880881</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-29</t>
+          <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 1</t>
+          <t xml:space="preserve">Tangshave 3</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13366,15 +13366,15 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H223">
-        <v>3416</v>
+        <v>1454</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880881</t>
+          <t xml:space="preserve">311880883</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 3</t>
+          <t xml:space="preserve">Tangshave 5</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13426,15 +13426,15 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H224">
-        <v>1454</v>
+        <v>725</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880883</t>
+          <t xml:space="preserve">311880886</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 5</t>
+          <t xml:space="preserve">Tangshave 6</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H225">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 6</t>
+          <t xml:space="preserve">Tangshave 7</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13546,11 +13546,11 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H226">
-        <v>725</v>
+        <v>501</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 7</t>
+          <t xml:space="preserve">Tangshave 8</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H227">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 8</t>
+          <t xml:space="preserve">Tangshave 9</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13661,20 +13661,20 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786913</t>
+          <t xml:space="preserve">9883339</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H228">
-        <v>501</v>
+        <v>758</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880886</t>
+          <t xml:space="preserve">311880882</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangshave 9</t>
+          <t xml:space="preserve">Egen Markvej 6</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13721,25 +13721,25 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883339</t>
+          <t xml:space="preserve">9151675</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H229">
-        <v>758</v>
+        <v>729</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880882</t>
+          <t xml:space="preserve">311884430</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-06</t>
+          <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13831,35 +13831,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egen Markvej 6</t>
+          <t xml:space="preserve">Hørup Bygade 44A</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6430</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9151675</t>
+          <t xml:space="preserve">308336, 308337</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H231">
-        <v>729</v>
+        <v>4431</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884428</t>
+          <t xml:space="preserve">311884501</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-26</t>
+          <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 10</t>
+          <t xml:space="preserve">Kettingvej 24A</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H240">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 20</t>
+          <t xml:space="preserve">Parkgade 15</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14441,20 +14441,20 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786709</t>
+          <t xml:space="preserve">8187423</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H241">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900368</t>
+          <t xml:space="preserve">311900365</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingvej 24A</t>
+          <t xml:space="preserve">Østergade 10</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H242">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 8</t>
+          <t xml:space="preserve">Østergade 20</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14561,20 +14561,20 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5786710</t>
+          <t xml:space="preserve">5786709</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H243">
-        <v>2009</v>
+        <v>300</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900366</t>
+          <t xml:space="preserve">311900368</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkgade 15</t>
+          <t xml:space="preserve">Østergade 8</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187423</t>
+          <t xml:space="preserve">5786710</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -14630,11 +14630,11 @@
         </is>
       </c>
       <c r="H244">
-        <v>299</v>
+        <v>2009</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900365</t>
+          <t xml:space="preserve">311900366</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15331,17 +15331,17 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejs Møllevej 15</t>
+          <t xml:space="preserve">Dyrkobbelgård Allé 4</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310</t>
+          <t xml:space="preserve">6300</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5277912</t>
+          <t xml:space="preserve">8527991</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -15350,11 +15350,11 @@
         </is>
       </c>
       <c r="H256">
-        <v>612</v>
+        <v>532</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914415</t>
+          <t xml:space="preserve">311914417</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsbjergvej 12</t>
+          <t xml:space="preserve">Nejs Møllevej 15</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6300</t>
+          <t xml:space="preserve">6310</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">8078774</t>
+          <t xml:space="preserve">5277912</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -15410,11 +15410,11 @@
         </is>
       </c>
       <c r="H257">
-        <v>720</v>
+        <v>612</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914414</t>
+          <t xml:space="preserve">311914415</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrkobbelgård Allé 4</t>
+          <t xml:space="preserve">Ravnsbjergvej 12</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8527991</t>
+          <t xml:space="preserve">8078774</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -15470,11 +15470,11 @@
         </is>
       </c>
       <c r="H258">
-        <v>532</v>
+        <v>720</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914417</t>
+          <t xml:space="preserve">311914414</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybølvej 2</t>
+          <t xml:space="preserve">Gerlachsgade 3</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15521,20 +15521,20 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280837</t>
+          <t xml:space="preserve">9022269</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H259">
-        <v>1089</v>
+        <v>624</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920147</t>
+          <t xml:space="preserve">311920169</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15571,30 +15571,30 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tandsbusk 2</t>
+          <t xml:space="preserve">Gerlachsgade 5A</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">6470</t>
+          <t xml:space="preserve">6400</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5290830</t>
+          <t xml:space="preserve">9022269</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H260">
-        <v>285</v>
+        <v>9768</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920174</t>
+          <t xml:space="preserve">311920169</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerlachsgade 5A</t>
+          <t xml:space="preserve">Nybølvej 2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15641,20 +15641,20 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022269</t>
+          <t xml:space="preserve">5280837</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H261">
-        <v>9768</v>
+        <v>1089</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920155</t>
+          <t xml:space="preserve">311920147</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15691,30 +15691,30 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerlachsgade 3</t>
+          <t xml:space="preserve">Tandsbusk 2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6400</t>
+          <t xml:space="preserve">6470</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9022269</t>
+          <t xml:space="preserve">5290830</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H262">
-        <v>624</v>
+        <v>285</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920155</t>
+          <t xml:space="preserve">311920174</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">

--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086987</t>
+          <t xml:space="preserve">311086983</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">

--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -5274,7 +5274,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560181</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560185</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560182</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560184</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560183</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560183</t>
+          <t xml:space="preserve">311560187</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674038</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809346</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809350</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809348</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809353</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809345</t>
+          <t xml:space="preserve">311809351</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874514</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874504</t>
+          <t xml:space="preserve">311874514</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884430</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884427</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">

--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L265"/>
+  <dimension ref="A1:M265"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-01-15</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-09</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-17</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-16</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-17</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-18</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-07</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-17</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-09</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-30</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-08</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-31</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-13</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-06-27</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-03-10</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4554,20 +4929,25 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086983</t>
+          <t xml:space="preserve">311086987</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-12-08</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-06</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-11</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-26</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-19</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-07</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6474,20 +7009,25 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674030</t>
+          <t xml:space="preserve">311674034</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6534,20 +7074,25 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674030</t>
+          <t xml:space="preserve">311674034</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6594,20 +7139,25 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674030</t>
+          <t xml:space="preserve">311674034</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-28</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-09</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-04</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-05</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-20</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-21</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-24</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-31</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8814,20 +9544,25 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717581</t>
+          <t xml:space="preserve">311717580</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8874,20 +9609,25 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717585</t>
+          <t xml:space="preserve">311717580</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total-Tjek</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-24</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-28</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-27</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-25</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11574,20 +12534,25 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803369</t>
+          <t xml:space="preserve">311805471</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-19</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11934,20 +12924,25 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809351</t>
+          <t xml:space="preserve">311809346</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11994,20 +12989,25 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809351</t>
+          <t xml:space="preserve">311809350</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12054,20 +13054,25 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809351</t>
+          <t xml:space="preserve">311809348</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12174,20 +13184,25 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809351</t>
+          <t xml:space="preserve">311809345</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-03</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-05</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-10</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13074,20 +14159,25 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874514</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13134,20 +14224,25 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874514</t>
+          <t xml:space="preserve">311874504</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-22</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-29</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-06</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13734,20 +14874,25 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884429</t>
+          <t xml:space="preserve">311884428</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13794,20 +14939,25 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884429</t>
+          <t xml:space="preserve">311884427</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-26</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-27</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-26</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-11</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-19</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-20</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-28</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-24</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-24</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-24</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-13</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-13</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-13</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15534,20 +16824,25 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920169</t>
+          <t xml:space="preserve">311920155</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15594,20 +16889,25 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920169</t>
+          <t xml:space="preserve">311920155</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-19</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,21 +17219,26 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L265"/>
+  <autoFilter ref="A1:M265"/>
 </worksheet>
 </file>
--- a/public/exports/29189773.xlsx
+++ b/public/exports/29189773.xlsx
@@ -4929,7 +4929,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086987</t>
+          <t xml:space="preserve">311086983</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560181</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560185</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560182</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560184</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560187</t>
+          <t xml:space="preserve">311560183</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674034</t>
+          <t xml:space="preserve">311674030</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805471</t>
+          <t xml:space="preserve">311803369</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
